--- a/output/pdf_financials_xlsx/MIM.xlsx
+++ b/output/pdf_financials_xlsx/MIM.xlsx
@@ -3324,25 +3324,25 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.06474199999999999</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.06474199999999999</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.048091</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.21967</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.967057</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.147489</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.319387</v>
       </c>
     </row>
     <row r="93">
@@ -5672,7 +5672,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -6634,7 +6638,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -7376,7 +7384,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -7988,7 +8000,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MIM.xlsx
+++ b/output/pdf_financials_xlsx/MIM.xlsx
@@ -768,19 +768,19 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000264</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.014302</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.07609100000000001</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.033307</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.009221</v>
       </c>
     </row>
     <row r="13">
@@ -1267,19 +1267,19 @@
         <v>-0.07192</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.021727</v>
+        <v>-2.021991</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.58643</v>
+        <v>-3.600732</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-7.865198</v>
+        <v>-7.941289</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-7.479754</v>
+        <v>-7.513061</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-5.150217</v>
+        <v>-5.159438</v>
       </c>
     </row>
     <row r="28">
@@ -1329,19 +1329,19 @@
         <v>-0.07192</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.020313</v>
+        <v>-2.020577</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.585017</v>
+        <v>-3.599319</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-7.863785</v>
+        <v>-7.939876</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-7.478812</v>
+        <v>-7.512119</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-5.150217</v>
+        <v>-5.159438</v>
       </c>
     </row>
     <row r="30">
@@ -1366,19 +1366,19 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-10283.06102712882</v>
+        <v>-10284.40474372678</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-21588.6848127183</v>
+        <v>-21674.81030952668</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-71024.06972543352</v>
+        <v>-71711.30780346821</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-106157.7288857346</v>
+        <v>-106630.5039034776</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-63756.09061648924</v>
+        <v>-63870.24015845507</v>
       </c>
     </row>
     <row r="31">
@@ -1463,13 +1463,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.07031</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.324692</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.278757</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0.143854</v>
@@ -1525,13 +1525,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.07031</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.324692</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.278757</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0.143854</v>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
@@ -12886,7 +12886,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13538,7 +13538,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14092,7 +14092,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -14152,7 +14152,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -14760,7 +14760,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">

--- a/output/pdf_financials_xlsx/MIM.xlsx
+++ b/output/pdf_financials_xlsx/MIM.xlsx
@@ -3554,16 +3554,16 @@
         <v>0</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.001414</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.001413</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.001413</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.000942</v>
       </c>
       <c r="I100" s="3" t="n">
         <v>0</v>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">

--- a/output/pdf_financials_xlsx/MIM.xlsx
+++ b/output/pdf_financials_xlsx/MIM.xlsx
@@ -901,10 +901,10 @@
         <v>-7.865198</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-7.479754</v>
+        <v>-3.721031</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-5.150217</v>
+        <v>-5.084391</v>
       </c>
     </row>
     <row r="17">
@@ -932,10 +932,10 @@
         <v>4.000371</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>3.746159</v>
+        <v>-0.012564</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.065826</v>
       </c>
     </row>
     <row r="18">
@@ -1276,10 +1276,10 @@
         <v>-7.941289</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-7.513061</v>
+        <v>-3.754338</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-5.159438</v>
+        <v>-5.093612</v>
       </c>
     </row>
     <row r="28">
@@ -1338,10 +1338,10 @@
         <v>-7.939876</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-7.512119</v>
+        <v>-3.753396</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-5.159438</v>
+        <v>-5.093612</v>
       </c>
     </row>
     <row r="30">
@@ -1375,10 +1375,10 @@
         <v>-71711.30780346821</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-106630.5039034776</v>
+        <v>-53277.44499645138</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-63870.24015845507</v>
+        <v>-63055.36023768259</v>
       </c>
     </row>
     <row r="31">
@@ -1406,10 +1406,10 @@
         <v>-50.86166934386141</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-50.08398671934933</v>
+        <v>-0.3376483560604575</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-0</v>
+        <v>-1.294668329009315</v>
       </c>
     </row>
     <row r="32">
@@ -1565,19 +1565,19 @@
         <v>0</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0</v>
+        <v>0.003886</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0</v>
+        <v>0.0025</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0</v>
+        <v>0.002723</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0</v>
+        <v>0.004504</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0</v>
+        <v>0.018621</v>
       </c>
     </row>
     <row r="38">
@@ -2430,19 +2430,19 @@
         <v>0</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.976617</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.577089</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.624555</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.716404</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.892114</v>
       </c>
     </row>
     <row r="65">
@@ -2523,19 +2523,19 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.347392</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.049977</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.094795</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.226969</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.354895</v>
       </c>
     </row>
     <row r="68">
@@ -3870,13 +3870,13 @@
         <v>0</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.210146</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.359355</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.346932</v>
       </c>
     </row>
     <row r="111">
@@ -8374,7 +8374,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -8532,7 +8536,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -11056,7 +11064,11 @@
           <t>Finders warrants on private placement 14</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -13160,7 +13172,11 @@
           <t>Deferred income tax recovery 14</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -14428,7 +14444,11 @@
           <t>Deferred income tax recovery 15</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
